--- a/testdata/configurationUAT/data.xlsx
+++ b/testdata/configurationUAT/data.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13343" windowHeight="4956"/>
+    <workbookView windowWidth="22944" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="101">
   <si>
     <t>username</t>
   </si>
@@ -188,7 +188,16 @@
     <t>auth_current_account_owner_name</t>
   </si>
   <si>
-    <t>mirko.lekic@ibank</t>
+    <t>fee_RSD_Clean</t>
+  </si>
+  <si>
+    <t>fee_With_Space_RSD</t>
+  </si>
+  <si>
+    <t>fee_EUR_Clean</t>
+  </si>
+  <si>
+    <t>lekic23558@ibank</t>
   </si>
   <si>
     <t>uat</t>
@@ -224,21 +233,21 @@
     <t>Visa prepaid</t>
   </si>
   <si>
+    <t>4313 **** **** 0619</t>
+  </si>
+  <si>
+    <t>4431********0118</t>
+  </si>
+  <si>
+    <t>Visa revolving card</t>
+  </si>
+  <si>
+    <t>4176 **** **** 6236</t>
+  </si>
+  <si>
     <t>4313 **** **** 5309</t>
   </si>
   <si>
-    <t>4431********0118</t>
-  </si>
-  <si>
-    <t>Visa revolving card</t>
-  </si>
-  <si>
-    <t>4176 **** **** 2688</t>
-  </si>
-  <si>
-    <t>4431 **** **** 0118</t>
-  </si>
-  <si>
     <t>A vista depozitni račun</t>
   </si>
   <si>
@@ -296,22 +305,32 @@
     <t>205-9001015647000-10</t>
   </si>
   <si>
-    <t>Master Debit Contactless - STOJKA PEŠIĆ</t>
-  </si>
-  <si>
-    <t>5169********5796</t>
-  </si>
-  <si>
-    <t>Visa PrePaid - STOJKA PEŠIĆ</t>
-  </si>
-  <si>
-    <t>4313********5309</t>
+    <t>Visa PayWave - BOŽICA KOLAREVIĆ</t>
+  </si>
+  <si>
+    <t>4381 **** **** 0511</t>
+  </si>
+  <si>
+    <t>Visa Revolving Classic - BOŽICA KOLAREVIĆ</t>
+  </si>
+  <si>
+    <t>4176 **** **** 9367</t>
   </si>
   <si>
     <t>205-9001005222221-92</t>
   </si>
   <si>
     <t>MILENKA AĆIMOVIĆ</t>
+  </si>
+  <si>
+    <t>15,00 RSD</t>
+  </si>
+  <si>
+    <t>15,00
+RSD</t>
+  </si>
+  <si>
+    <t>0,00 EUR</t>
   </si>
 </sst>
 </file>
@@ -938,7 +957,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -948,6 +967,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -956,6 +978,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1493,10 +1518,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BB10"/>
+  <dimension ref="A1:BE12"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="17.712962962963" customWidth="1"/>
+    <col min="1" max="1" width="42.3333333333333" customWidth="1"/>
     <col min="2" max="2" width="10.5555555555556" customWidth="1"/>
     <col min="3" max="3" width="33.5740740740741" customWidth="1"/>
     <col min="5" max="6" width="22.1111111111111" customWidth="1"/>
@@ -1539,13 +1564,16 @@
     <col min="47" max="48" width="23.7777777777778" customWidth="1"/>
     <col min="49" max="49" width="37.7777777777778" customWidth="1"/>
     <col min="50" max="50" width="27.8888888888889" customWidth="1"/>
-    <col min="51" max="51" width="31.7777777777778" customWidth="1"/>
+    <col min="51" max="51" width="39.7777777777778" customWidth="1"/>
     <col min="52" max="52" width="27.8888888888889" customWidth="1"/>
     <col min="53" max="53" width="26.6666666666667" customWidth="1"/>
     <col min="54" max="54" width="34.2222222222222" customWidth="1"/>
+    <col min="55" max="55" width="19.8796296296296" style="3" customWidth="1"/>
+    <col min="56" max="56" width="21.5" style="3" customWidth="1"/>
+    <col min="57" max="57" width="18.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:54">
+    <row r="1" s="1" customFormat="1" spans="1:57">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1639,7 +1667,7 @@
       <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="4" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="1" t="s">
@@ -1690,16 +1718,16 @@
       <c r="AV1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="4" t="s">
+      <c r="AW1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="AX1" s="4" t="s">
+      <c r="AX1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AY1" s="4" t="s">
+      <c r="AY1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AZ1" s="4" t="s">
+      <c r="AZ1" s="5" t="s">
         <v>50</v>
       </c>
       <c r="BA1" s="1" t="s">
@@ -1708,1494 +1736,1591 @@
       <c r="BB1" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="BC1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:54">
-      <c r="A2" s="5" t="s">
-        <v>53</v>
+    <row r="2" s="2" customFormat="1" ht="28.8" spans="1:57">
+      <c r="A2" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N2" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="S2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="U2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="V2" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="W2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z2" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB2" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD2" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="X2" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB2" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD2" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="AF2" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH2" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="AH2" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ2" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="AJ2" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AO2" s="2">
         <v>73</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AQ2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AU2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AS2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AT2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AU2" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="AV2" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AW2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AX2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AY2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AZ2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
+      </c>
+      <c r="BC2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD2" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE2" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:54">
-      <c r="A3" s="5" t="s">
-        <v>53</v>
+    <row r="3" s="2" customFormat="1" ht="28.8" spans="1:57">
+      <c r="A3" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N3" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="S3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="U3" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="V3" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="W3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="X3" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z3" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB3" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD3" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="X3" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB3" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD3" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="AF3" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH3" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="AH3" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ3" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="AJ3" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="AK3" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AN3" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AO3" s="2">
         <v>73</v>
       </c>
       <c r="AP3" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AQ3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT3" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AU3" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AS3" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AT3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="AV3" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AW3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AX3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AY3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AZ3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="BA3" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="BB3" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD3" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:54">
-      <c r="A4" s="5" t="s">
-        <v>53</v>
+    <row r="4" s="2" customFormat="1" ht="28.8" spans="1:57">
+      <c r="A4" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N4" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="S4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="U4" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="V4" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="W4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="X4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z4" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB4" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD4" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="X4" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z4" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB4" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC4" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD4" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE4" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="AF4" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AG4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH4" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="AH4" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="AI4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ4" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="AJ4" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="AK4" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AL4" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AM4" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AN4" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AO4" s="2">
         <v>73</v>
       </c>
       <c r="AP4" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AQ4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT4" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AR4" s="2" t="s">
+      <c r="AU4" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AS4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AT4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AU4" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="AV4" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AW4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AX4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AY4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AZ4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="BA4" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="BB4" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
+      </c>
+      <c r="BC4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD4" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE4" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:54">
-      <c r="A5" s="5" t="s">
-        <v>53</v>
+    <row r="5" s="2" customFormat="1" ht="28.8" spans="1:57">
+      <c r="A5" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N5" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="S5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="U5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="V5" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="W5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="X5" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z5" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="X5" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z5" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB5" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD5" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE5" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="AF5" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH5" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="AH5" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ5" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="AJ5" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="AK5" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AN5" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AO5" s="2">
         <v>73</v>
       </c>
       <c r="AP5" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AQ5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AR5" s="2" t="s">
+      <c r="AU5" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AS5" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AT5" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AU5" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="AV5" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AW5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AX5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AY5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AZ5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="BA5" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="BB5" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
+      </c>
+      <c r="BC5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD5" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE5" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:54">
-      <c r="A6" s="5" t="s">
-        <v>53</v>
+    <row r="6" s="2" customFormat="1" ht="28.8" spans="1:57">
+      <c r="A6" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N6" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="S6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="U6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="V6" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="W6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="X6" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z6" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB6" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE6" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="X6" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z6" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB6" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD6" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE6" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="AF6" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AG6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH6" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="AH6" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ6" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="AJ6" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="AK6" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AL6" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AM6" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AN6" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AO6" s="2">
         <v>73</v>
       </c>
       <c r="AP6" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AQ6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT6" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AR6" s="2" t="s">
+      <c r="AU6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AS6" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AT6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AU6" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="AV6" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AW6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AX6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AY6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AZ6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="BA6" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="BB6" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
+      </c>
+      <c r="BC6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD6" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE6" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:54">
-      <c r="A7" s="5" t="s">
-        <v>53</v>
+    <row r="7" s="2" customFormat="1" ht="28.8" spans="1:57">
+      <c r="A7" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N7" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="S7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="U7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="V7" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="W7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="X7" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z7" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB7" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD7" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="X7" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z7" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB7" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD7" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE7" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="AF7" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AG7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH7" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="AH7" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ7" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="AJ7" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="AK7" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AL7" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AM7" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AN7" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AO7" s="2">
         <v>73</v>
       </c>
       <c r="AP7" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AQ7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT7" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AR7" s="2" t="s">
+      <c r="AU7" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AS7" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AT7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AU7" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="AV7" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AW7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AX7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AY7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AZ7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="BA7" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="BB7" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
+      </c>
+      <c r="BC7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE7" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:54">
-      <c r="A8" s="5" t="s">
-        <v>53</v>
+    <row r="8" s="2" customFormat="1" ht="28.8" spans="1:57">
+      <c r="A8" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N8" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="S8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="U8" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="V8" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="W8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="X8" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z8" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB8" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD8" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="X8" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z8" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB8" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD8" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE8" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="AF8" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AG8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH8" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="AH8" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ8" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="AJ8" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="AK8" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AL8" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AM8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AN8" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AO8" s="2">
         <v>73</v>
       </c>
       <c r="AP8" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AQ8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AR8" s="2" t="s">
+      <c r="AU8" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AS8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AT8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AU8" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="AV8" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AW8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AX8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AY8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AZ8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="BA8" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="BB8" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
+      </c>
+      <c r="BC8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD8" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE8" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:54">
-      <c r="A9" s="5" t="s">
-        <v>53</v>
+    <row r="9" s="2" customFormat="1" ht="28.8" spans="1:57">
+      <c r="A9" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N9" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="S9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="U9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="V9" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="W9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="X9" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z9" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB9" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD9" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="X9" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z9" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA9" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB9" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC9" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD9" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE9" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="AF9" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH9" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="AH9" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ9" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="AJ9" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AM9" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AN9" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AO9" s="2">
         <v>73</v>
       </c>
       <c r="AP9" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AQ9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT9" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AR9" s="2" t="s">
+      <c r="AU9" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AS9" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AT9" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AU9" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="AV9" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AW9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AX9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AY9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AZ9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="BA9" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="BB9" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
+      </c>
+      <c r="BC9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD9" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE9" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:54">
-      <c r="A10" s="5" t="s">
-        <v>53</v>
+    <row r="10" s="2" customFormat="1" ht="28.8" spans="1:57">
+      <c r="A10" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N10" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="S10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="U10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="V10" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="W10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="X10" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD10" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="X10" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z10" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA10" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB10" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC10" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD10" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE10" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="AF10" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH10" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="AH10" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ10" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="AJ10" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="AK10" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AL10" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AM10" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AN10" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AO10" s="2">
         <v>73</v>
       </c>
       <c r="AP10" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AQ10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT10" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AR10" s="2" t="s">
+      <c r="AU10" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AS10" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AT10" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AU10" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="AV10" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AW10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AX10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AY10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AZ10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="BA10" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="BB10" s="2" t="s">
-        <v>94</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="BC10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD10" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE10" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:57">
+      <c r="BD11" s="2"/>
+    </row>
+    <row r="12" spans="1:57">
+      <c r="BD12" s="2"/>
+      <c r="BE12" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="mirko.lekic@ibank" tooltip="mailto:mirko.lekic@ibank"/>
-    <hyperlink ref="A3" r:id="rId1" display="mirko.lekic@ibank" tooltip="mailto:mirko.lekic@ibank"/>
-    <hyperlink ref="A4" r:id="rId1" display="mirko.lekic@ibank" tooltip="mailto:mirko.lekic@ibank"/>
-    <hyperlink ref="A5" r:id="rId1" display="mirko.lekic@ibank" tooltip="mailto:mirko.lekic@ibank"/>
-    <hyperlink ref="A6" r:id="rId1" display="mirko.lekic@ibank" tooltip="mailto:mirko.lekic@ibank"/>
-    <hyperlink ref="A7" r:id="rId1" display="mirko.lekic@ibank" tooltip="mailto:mirko.lekic@ibank"/>
-    <hyperlink ref="A8" r:id="rId1" display="mirko.lekic@ibank" tooltip="mailto:mirko.lekic@ibank"/>
-    <hyperlink ref="A9" r:id="rId1" display="mirko.lekic@ibank" tooltip="mailto:mirko.lekic@ibank"/>
-    <hyperlink ref="A10" r:id="rId1" display="mirko.lekic@ibank" tooltip="mailto:mirko.lekic@ibank"/>
+    <hyperlink ref="A2" r:id="rId1" display="lekic23558@ibank" tooltip="mailto:lekic23558@ibank"/>
+    <hyperlink ref="A3" r:id="rId1" display="lekic23558@ibank" tooltip="mailto:lekic23558@ibank"/>
+    <hyperlink ref="A4" r:id="rId1" display="lekic23558@ibank" tooltip="mailto:lekic23558@ibank"/>
+    <hyperlink ref="A5" r:id="rId1" display="lekic23558@ibank" tooltip="mailto:lekic23558@ibank"/>
+    <hyperlink ref="A6" r:id="rId1" display="lekic23558@ibank" tooltip="mailto:lekic23558@ibank"/>
+    <hyperlink ref="A7" r:id="rId1" display="lekic23558@ibank" tooltip="mailto:lekic23558@ibank"/>
+    <hyperlink ref="A8" r:id="rId1" display="lekic23558@ibank" tooltip="mailto:lekic23558@ibank"/>
+    <hyperlink ref="A9" r:id="rId1" display="lekic23558@ibank" tooltip="mailto:lekic23558@ibank"/>
+    <hyperlink ref="A10" r:id="rId1" display="lekic23558@ibank" tooltip="mailto:lekic23558@ibank"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
